--- a/output/pdf_financials_xlsx/CAPR.xlsx
+++ b/output/pdf_financials_xlsx/CAPR.xlsx
@@ -2631,10 +2631,10 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.043509</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.24116</v>
       </c>
     </row>
     <row r="93">
@@ -4096,7 +4096,11 @@
           <t>Reserve for warrants 12</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CAPR.xlsx
+++ b/output/pdf_financials_xlsx/CAPR.xlsx
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.131408</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.071505</v>
       </c>
     </row>
     <row r="35">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.131408</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.071505</v>
       </c>
     </row>
     <row r="37">
@@ -1603,10 +1603,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.137972</v>
+        <v>0.006564</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.092141</v>
+        <v>0.020636</v>
       </c>
     </row>
     <row r="49">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/output/pdf_financials_xlsx/CAPR.xlsx
+++ b/output/pdf_financials_xlsx/CAPR.xlsx
@@ -1275,10 +1275,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C34" s="3" t="n">
+        <v>0.235699</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0.131408</v>
@@ -1298,10 +1296,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0</v>
@@ -1321,10 +1317,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C36" s="3" t="n">
+        <v>0.235699</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0.131408</v>
@@ -1344,10 +1338,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0</v>
@@ -1367,10 +1359,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
@@ -1390,10 +1380,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>0</v>
@@ -1413,10 +1401,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
@@ -1436,10 +1422,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C41" s="3" t="n">
+        <v>0.019747</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>0.014958</v>
@@ -1459,10 +1443,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>0</v>
@@ -1482,10 +1464,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>0</v>
@@ -1505,10 +1485,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>0</v>
@@ -1528,10 +1506,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>0</v>
@@ -1551,10 +1527,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>0</v>
@@ -1574,10 +1548,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>0</v>
@@ -1597,10 +1569,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C48" s="3" t="n">
+        <v>0.034606</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.006564</v>
@@ -1620,10 +1590,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C49" s="3" t="n">
+        <v>0.290052</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>0.15293</v>
@@ -1643,10 +1611,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>0</v>
@@ -1666,10 +1632,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>0</v>
@@ -1689,10 +1653,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>0</v>
@@ -1712,10 +1674,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0</v>
@@ -1735,10 +1695,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D54" s="3" t="n">
         <v>0</v>
@@ -1785,10 +1743,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>0</v>
@@ -1808,10 +1764,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>0</v>
@@ -1831,10 +1785,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C58" s="3" t="n">
+        <v>2.0716</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>1.989</v>
@@ -1854,10 +1806,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>0</v>
@@ -1877,10 +1827,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>0</v>
@@ -1900,10 +1848,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>0</v>
@@ -1923,10 +1869,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C62" s="3" t="n">
+        <v>2.0716</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>1.989</v>
@@ -1946,10 +1890,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C63" s="3" t="n">
+        <v>2.361652</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>2.14193</v>
@@ -1969,16 +1911,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C64" s="3" t="n">
+        <v>0.010886</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.099526</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.175287</v>
       </c>
     </row>
     <row r="65">
@@ -1992,10 +1932,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>0</v>
@@ -2015,10 +1953,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>0</v>
@@ -2038,16 +1974,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C67" s="3" t="n">
+        <v>0.201886</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.291099</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.125974</v>
       </c>
     </row>
     <row r="68">
@@ -2061,10 +1995,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C68" s="3" t="n">
+        <v>0.212772</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>0.390625</v>
@@ -2084,10 +2016,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>0</v>
@@ -2107,10 +2037,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>0</v>
@@ -2130,10 +2058,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>0</v>
@@ -2153,10 +2079,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D72" s="3" t="n">
         <v>0</v>
@@ -2176,10 +2100,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>0</v>
@@ -2199,10 +2121,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>0</v>
@@ -2222,10 +2142,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>0</v>
@@ -2272,10 +2190,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>0</v>
@@ -2295,10 +2211,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
         <v>0</v>
@@ -2318,10 +2232,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>0</v>
@@ -2368,10 +2280,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>0</v>
@@ -2391,10 +2301,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>0</v>
@@ -2414,10 +2322,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>0</v>
@@ -2437,10 +2343,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
         <v>0</v>
@@ -2460,10 +2364,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>0</v>
@@ -2510,10 +2412,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C87" s="3" t="n">
+        <v>0.212772</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>0.390625</v>
@@ -2533,10 +2433,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C88" s="3" t="n">
+        <v>3.605824</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>3.742065</v>
@@ -2556,10 +2454,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>0</v>
@@ -2579,10 +2475,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C90" s="3" t="n">
+        <v>-2.110784</v>
       </c>
       <c r="D90" s="3" t="n">
         <v>-2.20541</v>
@@ -2602,10 +2496,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>0</v>
@@ -2625,10 +2517,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C92" s="3" t="n">
+        <v>0.4085</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0.043509</v>
@@ -2648,10 +2538,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>0</v>
@@ -2671,10 +2559,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C94" s="3" t="n">
+        <v>2.14888</v>
       </c>
       <c r="D94" s="3" t="n">
         <v>1.751305</v>
@@ -2694,10 +2580,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>0</v>
@@ -2717,10 +2601,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C96" s="3" t="n">
+        <v>2.14888</v>
       </c>
       <c r="D96" s="3" t="n">
         <v>1.751305</v>
@@ -2740,10 +2622,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C97" s="3" t="n">
+        <v>0.9099054390740041</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>0.8176294276657033</v>
@@ -3553,7 +3433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3926,10 +3806,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F10" s="5" t="n">
+        <v>0.212772</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.390625</v>
@@ -4235,52 +4113,60 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Notes 31, 2025</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F19" s="5" t="n">
+        <v>0.235699</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.131408</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Receivables (Note 4)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>Receivables</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4289,34 +4175,36 @@
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.591268</v>
+        <v>0.019747</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.577325</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>-0.5597259999999999</v>
+        <v>0.014958</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Share-based payments 11</t>
+          <t>Prepaid expenses (Note 5)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>PrepaidAssets</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4324,49 +4212,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>0.1278</v>
+      <c r="F21" s="5" t="n">
+        <v>0.034606</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.006564</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Amended Option Agreement compensation 6</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Total Current Assets</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F22" s="5" t="n">
+        <v>0.290052</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.15293</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -4377,58 +4265,60 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 9</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>Exploration and evaluation assets (Notes 6, 8)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n">
-        <v>-0.1</v>
+      <c r="F23" s="5" t="n">
+        <v>2.0716</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>1.989</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Current Assets</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 6</t>
+          <t>Total Assets</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NetOtherInvestingChanges</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4436,13 +4326,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F24" s="5" t="n">
+        <v>2.361652</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.15401</v>
+        <v>2.14193</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -4453,54 +4341,60 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Current Liabilities</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items total</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities (Note 7)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-0.513416</v>
+        <v>0.212772</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.419815</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>-0.531926</v>
+        <v>0.390625</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Receivables 4</t>
+          <t>Share capital (Note 8)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4508,113 +4402,105 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F26" s="5" t="n">
+        <v>3.605824</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.004789</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>0.00368</v>
+        <v>3.742065</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prepaid expenses 5</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Reserve for restricted share units (Note 9)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F27" s="5" t="n">
+        <v>0.099027</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.028042</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>-0.014072</v>
+        <v>0.085368</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities 7</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
+          <t>Reserve for share-based payments (Note 10)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F28" s="5" t="n">
+        <v>0.146313</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.177853</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>0.110636</v>
+        <v>0.085773</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Net change in non-cash working capital items</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cash flows used in Operating Activities</t>
+          <t>Reserve for warrants (Note 11)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>AdditionalPaidInCapital</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4622,47 +4508,49 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F29" s="5" t="n">
+        <v>0.4085</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.209131</v>
-      </c>
-      <c r="H29" s="5" t="n">
-        <v>-0.431682</v>
+        <v>0.043509</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ackley property option 6</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>Accumulated deficit</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F30" s="5" t="n">
+        <v>-2.110784</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.02591</v>
+        <v>-2.20541</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -4673,22 +4561,22 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Investing Activities</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cash flows used in Investing Activities</t>
+          <t>Total Shareholders’ Equity</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4696,13 +4584,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F31" s="5" t="n">
+        <v>2.14888</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.02591</v>
+        <v>1.751305</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -4713,35 +4599,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Shareholders’ Equity</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Proceeds from private placements 8,9,12</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Total Liabilities and Shareholders’ Equity</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F32" s="5" t="n">
+        <v>2.361652</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.13075</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0.371779</v>
+        <v>2.14193</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -4750,21 +4640,13 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Financing Activities</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cash flows from Financing Activities</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Notes 31, 2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -4776,10 +4658,10 @@
         </is>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.13075</v>
+        <v>0.002024</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.371779</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="34">
@@ -4790,17 +4672,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Increase (decrease) in cash</t>
+          <t>Net loss for the year</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4808,16 +4690,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F34" s="5" t="n">
+        <v>-0.591268</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.104291</v>
+        <v>-0.577325</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>-0.059903</v>
+        <v>-0.5597259999999999</v>
       </c>
     </row>
     <row r="35">
@@ -4828,17 +4708,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
+          <t>Share-based payments 11</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4846,14 +4726,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F35" s="5" t="n">
-        <v>0.689889</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0.235699</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.131408</v>
+        <v>0.1278</v>
       </c>
     </row>
     <row r="36">
@@ -4864,32 +4748,32 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Amended Option Agreement compensation 6</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F36" s="5" t="n">
-        <v>0.235699</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.131408</v>
-      </c>
-      <c r="H36" s="5" t="n">
-        <v>0.071505</v>
+        <v>0.0035</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -4905,31 +4789,27 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 9 and 10)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement 9</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F37" s="5" t="n">
-        <v>0.06685199999999999</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H37" s="5" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="38">
@@ -4945,10 +4825,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Amended Option Agreement Compensation (Note 6)</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Impairment of exploration and evaluation assets 6</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -4960,7 +4844,7 @@
         </is>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.15401</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -4981,29 +4865,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Impairment of Exploration and Evaluation Assets (Note 6)</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>NetOtherInvestingChanges</t>
-        </is>
-      </c>
+          <t>Adjustments for non-cash items total</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.011</v>
+        <v>-0.513416</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.15401</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.419815</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>-0.531926</v>
       </c>
     </row>
     <row r="40">
@@ -5019,7 +4897,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Receivables (Note 4)</t>
+          <t>Receivables 4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5032,16 +4910,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F40" s="5" t="n">
-        <v>-0.000655</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G40" s="5" t="n">
         <v>0.004789</v>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H40" s="5" t="n">
+        <v>0.00368</v>
       </c>
     </row>
     <row r="41">
@@ -5057,7 +4935,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Prepaid expenses (Note 5)</t>
+          <t>Prepaid expenses 5</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5070,16 +4948,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F41" s="5" t="n">
-        <v>0.002609</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G41" s="5" t="n">
         <v>0.028042</v>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H41" s="5" t="n">
+        <v>-0.014072</v>
       </c>
     </row>
     <row r="42">
@@ -5095,7 +4973,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Note 7)</t>
+          <t>Accounts payable and accrued liabilities 7</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5108,16 +4986,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F42" s="5" t="n">
-        <v>0.08787200000000001</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G42" s="5" t="n">
         <v>0.177853</v>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H42" s="5" t="n">
+        <v>0.110636</v>
       </c>
     </row>
     <row r="43">
@@ -5133,7 +5011,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cash Flows (used in) Operating Activities</t>
+          <t>Cash flows used in Operating Activities</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5146,16 +5024,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>-0.42359</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G43" s="5" t="n">
         <v>-0.209131</v>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H43" s="5" t="n">
+        <v>-0.431682</v>
       </c>
     </row>
     <row r="44">
@@ -5171,7 +5049,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ackley property option (Note 6)</t>
+          <t>Ackley property option 6</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -5180,8 +5058,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F44" s="5" t="n">
-        <v>-0.0306</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G44" s="5" t="n">
         <v>-0.02591</v>
@@ -5205,7 +5085,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cash Flows (used in) Investing Activities</t>
+          <t>Cash flows used in Investing Activities</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5218,8 +5098,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F45" s="5" t="n">
-        <v>-0.0306</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G45" s="5" t="n">
         <v>-0.02591</v>
@@ -5243,7 +5125,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Proceeds from private placements (Note 8)</t>
+          <t>Proceeds from private placements 8,9,12</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -5260,10 +5142,8 @@
       <c r="G46" s="5" t="n">
         <v>0.13075</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H46" s="5" t="n">
+        <v>0.371779</v>
       </c>
     </row>
     <row r="47">
@@ -5279,7 +5159,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cash Flows from Financing Activities</t>
+          <t>Cash flows from Financing Activities</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5300,10 +5180,8 @@
       <c r="G47" s="5" t="n">
         <v>0.13075</v>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H47" s="5" t="n">
+        <v>0.371779</v>
       </c>
     </row>
     <row r="48">
@@ -5319,7 +5197,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>(Decrease) in cash</t>
+          <t>Increase (decrease) in cash</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5332,130 +5210,144 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F48" s="5" t="n">
-        <v>-0.45419</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G48" s="5" t="n">
         <v>-0.104291</v>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H48" s="5" t="n">
+        <v>-0.059903</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Financing Activities</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Notes 31, 2025</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F49" s="5" t="n">
+        <v>0.689889</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.002024</v>
+        <v>0.235699</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.131408</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Professional fees 15</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>Cash, end of year</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F50" s="5" t="n">
+        <v>0.235699</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.274755</v>
+        <v>0.131408</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.273325</v>
+        <v>0.071505</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures 6</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Share-based compensation (Notes 9 and 10)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.082221</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>0.146005</v>
+      <c r="F51" s="5" t="n">
+        <v>0.06685199999999999</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Shareholder costs</t>
+          <t>Amended Option Agreement Compensation (Note 6)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
@@ -5464,177 +5356,203 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F52" s="5" t="n">
-        <v>0.021225</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.020594</v>
-      </c>
-      <c r="H52" s="5" t="n">
-        <v>0.03247</v>
+        <v>0.0035</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Office and general</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Impairment of Exploration and Evaluation Assets (Note 6)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.036538</v>
+        <v>0.011</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.018197</v>
-      </c>
-      <c r="H53" s="5" t="n">
-        <v>0.012128</v>
+        <v>0.15401</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Advertising and promotion</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
+          <t>Receivables (Note 4)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.012187</v>
+        <v>-0.000655</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.012738</v>
-      </c>
-      <c r="H54" s="5" t="n">
-        <v>0.064774</v>
+        <v>0.004789</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Travel and entertainment</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>Prepaid expenses (Note 5)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.024837</v>
+        <v>0.002609</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.01481</v>
-      </c>
-      <c r="H55" s="5" t="n">
-        <v>0.003224</v>
+        <v>0.028042</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Share-based payments 11, 15</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities (Note 7)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="n">
-        <v>0.1278</v>
+      <c r="F56" s="5" t="n">
+        <v>0.08787200000000001</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.177853</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets 6</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
+          <t>Cash Flows (used in) Operating Activities</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F57" s="5" t="n">
+        <v>-0.42359</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.15401</v>
+        <v>-0.209131</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -5645,17 +5563,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Total Expenses</t>
+          <t>Ackley property option (Note 6)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -5664,68 +5582,70 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F58" s="5" t="n">
+        <v>-0.0306</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.577325</v>
-      </c>
-      <c r="H58" s="5" t="n">
-        <v>0.659726</v>
+        <v>-0.02591</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other Income / (Expenses)</t>
+          <t>Investing Activities</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gain on debt settlement 9, 15</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Cash Flows (used in) Investing Activities</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>0.1</v>
+      <c r="F59" s="5" t="n">
+        <v>-0.0306</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.02591</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Other Income / (Expenses)</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Total Other Income</t>
+          <t>Proceeds from private placements (Note 8)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -5739,32 +5659,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>0.1</v>
+      <c r="G60" s="5" t="n">
+        <v>0.13075</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Other Income / (Expenses)</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Cash Flows from Financing Activities</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -5776,44 +5700,50 @@
         </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.577325</v>
-      </c>
-      <c r="H61" s="5" t="n">
-        <v>-0.5597259999999999</v>
+        <v>0.13075</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Outstanding Shares</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>- Basic and diluted 13</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>(Decrease) in cash</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F62" s="5" t="n">
+        <v>-0.45419</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>42.511343</v>
-      </c>
-      <c r="H62" s="5" t="n">
-        <v>67.860619</v>
+        <v>-0.104291</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -5822,14 +5752,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Loss per Share</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>- Basic and diluted 13</t>
+          <t>Notes 31, 2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -5844,10 +5770,10 @@
         </is>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-1.4e-08</v>
+        <v>0.002024</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>-8e-09</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="64">
@@ -5858,12 +5784,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Balance, September 1, 2023 41,672,500 3,605,824 - 99,027 146,313 408,500</t>
+          <t>Professional fees 15</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -5878,10 +5804,10 @@
         </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>2.14888</v>
+        <v>0.274755</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>-2.110784</v>
+        <v>0.273325</v>
       </c>
     </row>
     <row r="65">
@@ -5892,12 +5818,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Shares issued on Ackley property option acquisition 1,300,000 45,500 - - - -</t>
+          <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
@@ -5912,12 +5838,10 @@
         </is>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0455</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.082221</v>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>0.146005</v>
       </c>
     </row>
     <row r="66">
@@ -5928,12 +5852,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Shares issued on amended option agreement 100,000 3,500 - - - -</t>
+          <t>Shareholder costs</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -5942,18 +5866,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F66" s="5" t="n">
+        <v>0.021225</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.020594</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>0.03247</v>
       </c>
     </row>
     <row r="67">
@@ -5964,12 +5884,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Shares issued on private placement 8,716,667 87,241 - - - 43,509</t>
+          <t>Office and general</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -5978,18 +5898,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F67" s="5" t="n">
+        <v>0.036538</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.13075</v>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.018197</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>0.012128</v>
       </c>
     </row>
     <row r="68">
@@ -6000,12 +5916,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Expiry of RSUs - - - (13,659) - -</t>
+          <t>Advertising and promotion</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -6014,18 +5930,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F68" s="5" t="n">
+        <v>0.012187</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.012738</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>0.013659</v>
+        <v>0.064774</v>
       </c>
     </row>
     <row r="69">
@@ -6036,12 +5948,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Expiry of options - - - - (60,540) -</t>
+          <t>Travel and entertainment</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -6050,18 +5962,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F69" s="5" t="n">
+        <v>0.024837</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.01481</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.06054</v>
+        <v>0.003224</v>
       </c>
     </row>
     <row r="70">
@@ -6072,12 +5980,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Expiry of warrants - - - - - (408,500)</t>
+          <t>Share-based payments 11, 15</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -6097,7 +6005,7 @@
         </is>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.4085</v>
+        <v>0.1278</v>
       </c>
     </row>
     <row r="71">
@@ -6108,12 +6016,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - - -</t>
+          <t>Impairment of exploration and evaluation assets 6</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -6128,10 +6036,12 @@
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>-0.577325</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>-0.577325</v>
+        <v>0.15401</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -6142,12 +6052,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Balance, August 31, 2024 51,789,167 3,742,065 - 85,368 85,773 43,509</t>
+          <t>Total Expenses</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -6162,10 +6072,10 @@
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>1.751305</v>
+        <v>0.577325</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>-2.20541</v>
+        <v>0.659726</v>
       </c>
     </row>
     <row r="73">
@@ -6176,12 +6086,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other Income / (Expenses)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Balance, September 1, 2024 51,789,167 3,742,065 - 85,368 85,773 43,509</t>
+          <t>Gain on debt settlement 9, 15</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
@@ -6195,11 +6105,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G73" s="5" t="n">
-        <v>1.751305</v>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H73" s="5" t="n">
-        <v>-2.20541</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="74">
@@ -6210,12 +6122,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other Income / (Expenses)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Proceeds from private placement 9 11,685,000 150,304 - - - 141,821</t>
+          <t>Total Other Income</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
@@ -6229,13 +6141,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G74" s="5" t="n">
-        <v>0.292125</v>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="75">
@@ -6246,12 +6158,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other Income / (Expenses)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Proceeds from shares to be issued - - 30,000 - - -</t>
+          <t>Net Loss and Comprehensive Loss</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -6266,12 +6178,10 @@
         </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.577325</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>-0.5597259999999999</v>
       </c>
     </row>
     <row r="76">
@@ -6282,12 +6192,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Weighted Average Number of Outstanding Shares</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Proceeds from flow-through private placement 9 2,875,000 59,170 - - - 55,830</t>
+          <t>- Basic and diluted 13</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -6302,12 +6212,10 @@
         </is>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>42.511343</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>67.860619</v>
       </c>
     </row>
     <row r="77">
@@ -6318,12 +6226,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Loss per Share</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Share issuance costs 9 - (70,229) - - 4,883 -</t>
+          <t>- Basic and diluted 13</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -6338,12 +6246,10 @@
         </is>
       </c>
       <c r="G77" s="5" t="n">
-        <v>-0.065346</v>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.4e-08</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>-8e-09</v>
       </c>
     </row>
     <row r="78">
@@ -6359,7 +6265,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Issuance on Destiny property acquisition agreement 6,9 8,000,000 160,000 - - - -</t>
+          <t>Balance, September 1, 2023 41,672,500 3,605,824 - 99,027 146,313 408,500</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
@@ -6374,12 +6280,10 @@
         </is>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.14888</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>-2.110784</v>
       </c>
     </row>
     <row r="79">
@@ -6395,7 +6299,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Issuance on debt conversion agreement 9 2,000,000 100,000 - - - -</t>
+          <t>Shares issued on Ackley property option acquisition 1,300,000 45,500 - - - -</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6410,7 +6314,7 @@
         </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.1</v>
+        <v>0.0455</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -6431,7 +6335,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Share-based compensation 11 - - - - 127,800 -</t>
+          <t>Shares issued on amended option agreement 100,000 3,500 - - - -</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -6446,7 +6350,7 @@
         </is>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.1278</v>
+        <v>0.0035</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -6467,7 +6371,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Balance, August 31, 2025 76,349,167 4,141,310 30,000 85,368 218,456 241,160</t>
+          <t>Shares issued on private placement 8,716,667 87,241 - - - 43,509</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
@@ -6482,10 +6386,12 @@
         </is>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1.951158</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>-2.765136</v>
+        <v>0.13075</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -6496,12 +6402,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Professional fees (Note 14)</t>
+          <t>Expiry of RSUs - - - (13,659) - -</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
@@ -6510,16 +6416,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F82" s="5" t="n">
-        <v>0.347093</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>0.274755</v>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>0.013659</v>
       </c>
     </row>
     <row r="83">
@@ -6530,12 +6438,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Note 6)</t>
+          <t>Expiry of options - - - - (60,540) -</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
@@ -6544,16 +6452,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F83" s="5" t="n">
-        <v>0.071536</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>0.082221</v>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0.06054</v>
       </c>
     </row>
     <row r="84">
@@ -6564,12 +6474,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 9, 10 and 14)</t>
+          <t>Expiry of warrants - - - - - (408,500)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -6578,18 +6488,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F84" s="5" t="n">
-        <v>0.06685199999999999</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H84" s="5" t="n">
+        <v>0.4085</v>
       </c>
     </row>
     <row r="85">
@@ -6600,12 +6510,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Impairment of Exploration and Evaluation Assets (Note 6)</t>
+          <t>Net loss for the year - - - - - -</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -6614,16 +6524,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>0.011</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.15401</v>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.577325</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>-0.577325</v>
       </c>
     </row>
     <row r="86">
@@ -6634,12 +6544,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Net Loss and Comprehensive Loss</t>
+          <t>Balance, August 31, 2024 51,789,167 3,742,065 - 85,368 85,773 43,509</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
@@ -6648,16 +6558,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F86" s="5" t="n">
-        <v>-0.591268</v>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G86" s="5" t="n">
-        <v>-0.577325</v>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.751305</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>-2.20541</v>
       </c>
     </row>
     <row r="87">
@@ -6668,12 +6578,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Outstanding Shares</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>– Basic and diluted</t>
+          <t>Balance, September 1, 2024 51,789,167 3,742,065 - 85,368 85,773 43,509</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -6682,16 +6592,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F87" s="5" t="n">
-        <v>41.102637</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G87" s="5" t="n">
-        <v>42.511343</v>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.751305</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>-2.20541</v>
       </c>
     </row>
     <row r="88">
@@ -6702,12 +6612,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Outstanding Shares</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Net Loss per Share – Basic and diluted (Note 12)</t>
+          <t>Proceeds from private placement 9 11,685,000 150,304 - - - 141,821</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6716,11 +6626,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F88" s="5" t="n">
-        <v>-1.4e-08</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G88" s="5" t="n">
-        <v>-1.4e-08</v>
+        <v>0.292125</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -6741,7 +6653,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Balance, September 1, 2022 40,372,500 3,553,824 74,722 131,118 408,500</t>
+          <t>Proceeds from shares to be issued - - 30,000 - - -</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -6750,11 +6662,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F89" s="5" t="n">
-        <v>2.621296</v>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-1.546868</v>
+        <v>0.03</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -6775,7 +6689,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Shares issued on Ackley Property option acquisition 6, 8 1,300,000 52,000 - - -</t>
+          <t>Proceeds from flow-through private placement 9 2,875,000 59,170 - - - 55,830</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -6784,13 +6698,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F90" s="5" t="n">
-        <v>0.052</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.115</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6811,7 +6725,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Share-based compensation 9, 10 - - 24,305 42,547 -</t>
+          <t>Share issuance costs 9 - (70,229) - - 4,883 -</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -6820,13 +6734,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>0.06685199999999999</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-0.065346</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6847,7 +6761,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cancellation of options 10 - - - (27,352) -</t>
+          <t>Issuance on Destiny property acquisition agreement 6,9 8,000,000 160,000 - - - -</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -6862,7 +6776,7 @@
         </is>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.027352</v>
+        <v>0.16</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -6883,7 +6797,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Net loss for the year - - - - -</t>
+          <t>Issuance on debt conversion agreement 9 2,000,000 100,000 - - - -</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -6892,11 +6806,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F93" s="5" t="n">
-        <v>-0.591268</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G93" s="5" t="n">
-        <v>-0.591268</v>
+        <v>0.1</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -6917,7 +6833,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Balance, August 31, 2023 41,672,500 3,605,824 99,027 146,313 408,500</t>
+          <t>Share-based compensation 11 - - - - 127,800 -</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -6926,11 +6842,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>2.14888</v>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-2.110784</v>
+        <v>0.1278</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -6951,7 +6869,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Balance, September 1, 2023 41,672,500 3,605,824 99,027 146,313 408,500</t>
+          <t>Balance, August 31, 2025 76,349,167 4,141,310 30,000 85,368 218,456 241,160</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -6960,16 +6878,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F95" s="5" t="n">
-        <v>2.14888</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-2.110784</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.951158</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>-2.765136</v>
       </c>
     </row>
     <row r="96">
@@ -6980,12 +6898,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Shares issued on Ackley Property option acquisition 6, 8 1,300,000 45,500 - - -</t>
+          <t>Professional fees (Note 14)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -6995,12 +6913,10 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.0455</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.347093</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.274755</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -7016,12 +6932,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Shares issued on Amended Option Agreement 6, 8 100,000 3,500 - - -</t>
+          <t>Exploration and evaluation expenditures (Note 6)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7031,12 +6947,10 @@
         </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.071536</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.082221</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -7052,12 +6966,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Shares issued on Private Placement 8,716,667 87,241 - - 43,509</t>
+          <t>Share-based compensation (Notes 9, 10 and 14)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -7067,7 +6981,7 @@
         </is>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.13075</v>
+        <v>0.06685199999999999</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -7088,12 +7002,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Expiry of RSUs 9 - - (13,659) - -</t>
+          <t>Impairment of Exploration and Evaluation Assets (Note 6)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -7102,13 +7016,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="5" t="n">
+        <v>0.011</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.013659</v>
+        <v>0.15401</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -7124,12 +7036,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Expiry of options 10 - - - (60,540) -</t>
+          <t>Net Loss and Comprehensive Loss</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7138,13 +7050,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F100" s="5" t="n">
+        <v>-0.591268</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.06054</v>
+        <v>-0.577325</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -7160,12 +7070,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Weighted Average Number of Outstanding Shares</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Expiry of warrants 11 - - - - (408,500)</t>
+          <t>– Basic and diluted</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7174,13 +7084,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F101" s="5" t="n">
+        <v>41.102637</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.4085</v>
+        <v>42.511343</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -7196,12 +7104,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Weighted Average Number of Outstanding Shares</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Balance, August 31, 2024 51,789,167 3,742,065 85,368 85,773 43,509</t>
+          <t>Net Loss per Share – Basic and diluted (Note 12)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -7211,12 +7119,506 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
+        <v>-1.4e-08</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-1.4e-08</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Balance, September 1, 2022 40,372,500 3,553,824 74,722 131,118 408,500</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>2.621296</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>-1.546868</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Shares issued on Ackley Property option acquisition 6, 8 1,300,000 52,000 - - -</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Share-based compensation 9, 10 - - 24,305 42,547 -</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>0.06685199999999999</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Cancellation of options 10 - - - (27,352) -</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.027352</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - - -</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>-0.591268</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>-0.591268</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2023 41,672,500 3,605,824 99,027 146,313 408,500</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>2.14888</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>-2.110784</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Balance, September 1, 2023 41,672,500 3,605,824 99,027 146,313 408,500</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>2.14888</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>-2.110784</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Shares issued on Ackley Property option acquisition 6, 8 1,300,000 45,500 - - -</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0.0455</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Shares issued on Amended Option Agreement 6, 8 100,000 3,500 - - -</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Shares issued on Private Placement 8,716,667 87,241 - - 43,509</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>0.13075</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Expiry of RSUs 9 - - (13,659) - -</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0.013659</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Expiry of options 10 - - - (60,540) -</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.06054</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Expiry of warrants 11 - - - - (408,500)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Balance, August 31, 2024 51,789,167 3,742,065 85,368 85,773 43,509</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="n">
         <v>1.751305</v>
       </c>
-      <c r="G102" s="5" t="n">
+      <c r="G116" s="5" t="n">
         <v>-2.20541</v>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>-</t>
         </is>
